--- a/data/trans_orig/IP07C06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>43235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>56750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34442</t>
+          <t>34589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45115</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>38559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37184</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>25236</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55764</t>
+          <t>54782</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>43945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57455</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89324</t>
+          <t>88903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109930</t>
+          <t>109559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48538</t>
+          <t>47967</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79124</t>
+          <t>78676</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>28789</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>52916</t>
+          <t>52514</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55761</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>67298</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>93725</t>
+          <t>93933</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>48942</t>
+          <t>48773</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>70698</t>
+          <t>69948</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>34149</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>53965</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>87768</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>118640</t>
+          <t>118916</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>150187</t>
+          <t>151094</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>175774</t>
+          <t>175217</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>184276</t>
+          <t>184879</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>209770</t>
+          <t>210390</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>343651</t>
+          <t>342236</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>378479</t>
+          <t>378856</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24121</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>24740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>43241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>30410</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45183</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69067</t>
+          <t>68655</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103912</t>
+          <t>103366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124063</t>
+          <t>124166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38444</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>45673</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67666</t>
+          <t>67007</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87477</t>
+          <t>86914</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36615</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30929</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>53664</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>77819</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>107085</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>58753</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>84832</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>47849</t>
+          <t>49224</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>70981</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>115206</t>
+          <t>114749</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>149277</t>
+          <t>149747</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>149329</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>177869</t>
+          <t>176478</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>159127</t>
+          <t>159496</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>187775</t>
+          <t>187321</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>316440</t>
+          <t>318401</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>357779</t>
+          <t>359190</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33885</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47841</t>
+          <t>47991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>24369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>64629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>23910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>25748</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29384</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56343</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73414</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110134</t>
+          <t>109893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134314</t>
+          <t>133415</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12798</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44192</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43400</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65173</t>
+          <t>65333</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21649</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36238</t>
+          <t>35834</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54925</t>
+          <t>55054</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>50965</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>50514</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>66949</t>
+          <t>66451</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>94428</t>
+          <t>94222</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>74996</t>
+          <t>74950</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>72244</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>99243</t>
+          <t>97793</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>133019</t>
+          <t>130922</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>167608</t>
+          <t>166710</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>174421</t>
+          <t>172871</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>204433</t>
+          <t>201879</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>167390</t>
+          <t>168581</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>199880</t>
+          <t>197933</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>350511</t>
+          <t>350254</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>390308</t>
+          <t>392529</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
